--- a/docs/contracts/fixtures/synthetic-lead-import-v1.xlsx
+++ b/docs/contracts/fixtures/synthetic-lead-import-v1.xlsx
@@ -172,6 +172,16 @@
           <t>Sample City</t>
         </is>
       </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Asked for a follow-up email</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Sam Example</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">

--- a/docs/contracts/fixtures/synthetic-lead-import-v1.xlsx
+++ b/docs/contracts/fixtures/synthetic-lead-import-v1.xlsx
@@ -56,22 +56,37 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>Region Sample</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Province Sample</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
           <t>Harborview Clinic</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Sam Example</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>0917 000 0199</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
         <is>
           <t>harborview@example.test</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>0917 000 0199</t>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Sample Street</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Sample City</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -98,10 +113,15 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>Region Sample</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
           <t/>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>missing-facility@example.test</t>
         </is>
@@ -115,17 +135,22 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>Region Sample</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
           <t>Pinecrest Clinic</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>0917 000 0202</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
         <is>
           <t>pinecrest@example.test</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>0917 000 0202</t>
         </is>
       </c>
     </row>
